--- a/BWI/bestwine_output/bestwine_Mauritius.xlsx
+++ b/BWI/bestwine_output/bestwine_Mauritius.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA42"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5142,6 +5142,224 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Amgo Beverages</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Amgo Beverages</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>42837</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Ebene</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>4th Floor, Ebene Skies, Rue de L’Institut</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>80817</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://amgobev.com</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>info@amgobev.com</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>+230 269 3700</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>C135323</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/amgo-beverages/</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/amgobeverages/</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amgo.beverages/</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>Angelica M</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative Italian Wines</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/angelica-m-frittitta-0696116/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Amgo Beverages</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Amgo Beverages</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>42837</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Ebene</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>4th Floor, Ebene Skies, Rue de L’Institut</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>80817</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://amgobev.com</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>info@amgobev.com</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>+230 269 3700</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>C135323</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/amgo-beverages/</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/amgobeverages/</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amgo.beverages/</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>Alma Henning</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>Wine Sales Manager And Product Development</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alma-henning-6177884/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
